--- a/Strategic_Theater_Summary_ReportT.xlsx
+++ b/Strategic_Theater_Summary_ReportT.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Johnn\Documents\LinkedInPD\PowerBITables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{56DE7F79-3055-43B7-94B8-1273FD31B248}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1CED05D5-984E-4B2D-A2BF-889B309CF07A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{FD381A36-D026-45DB-A62C-D1FD675EA112}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t>OCONUS-EUROPE</t>
   </si>
   <si>
-    <t>Strategic Command Sector</t>
-  </si>
-  <si>
     <t>Total Deployed Combat Units</t>
   </si>
   <si>
@@ -56,6 +53,9 @@
   </si>
   <si>
     <t>Theater Readiness Assessment</t>
+  </si>
+  <si>
+    <t>Region</t>
   </si>
 </sst>
 </file>
@@ -715,18 +715,6 @@
   </cellStyles>
   <dxfs count="10">
     <dxf>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="thin">
-          <color indexed="64"/>
-        </left>
-        <right style="thin">
-          <color indexed="64"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
       <border diagonalUp="0" diagonalDown="0">
         <left style="thin">
           <color indexed="64"/>
@@ -843,6 +831,15 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <right style="thin">
+          <color indexed="64"/>
+        </right>
+        <top style="thin">
+          <color indexed="64"/>
+        </top>
         <bottom style="thin">
           <color indexed="64"/>
         </bottom>
@@ -850,18 +847,21 @@
     </dxf>
     <dxf>
       <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
         <right style="thin">
           <color indexed="64"/>
         </right>
-        <top style="thin">
-          <color indexed="64"/>
-        </top>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
+        <top/>
+        <bottom/>
       </border>
     </dxf>
   </dxfs>
@@ -878,15 +878,15 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2921A316-5F8D-4D87-999A-CEBDC86D21C4}" name="Table1" displayName="Table1" ref="A1:F5" totalsRowShown="0" headerRowDxfId="0" headerRowBorderDxfId="8" tableBorderDxfId="9" totalsRowBorderDxfId="7">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2921A316-5F8D-4D87-999A-CEBDC86D21C4}" name="Table1" displayName="Table1" ref="A1:F5" totalsRowShown="0" headerRowDxfId="9" headerRowBorderDxfId="8" tableBorderDxfId="7" totalsRowBorderDxfId="6">
   <autoFilter ref="A1:F5" xr:uid="{2921A316-5F8D-4D87-999A-CEBDC86D21C4}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{6A730CF5-2A6C-4305-B125-C29D56F2D199}" name="Strategic Command Sector" dataDxfId="6"/>
-    <tableColumn id="2" xr3:uid="{7A6C1557-9973-4EDC-9C24-05049FF28A3E}" name="Total Deployed Combat Units" dataDxfId="5"/>
-    <tableColumn id="3" xr3:uid="{5DBF8A7C-4F69-4778-B446-4FD13850CE7C}" name="Total Cumulative Inventory Items" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{FAB7F246-DBFE-48B7-9D0E-62F04D72EF5E}" name="Total Cumulative Maintenance Hours" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{3FAA3011-47B9-49E2-BE83-98BABA45CEF4}" name="Average Theater Intensity Ratio" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{AD53D50A-40C7-4504-85C0-88E6A1BF1A92}" name="Theater Readiness Assessment" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{6A730CF5-2A6C-4305-B125-C29D56F2D199}" name="Region" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{7A6C1557-9973-4EDC-9C24-05049FF28A3E}" name="Total Deployed Combat Units" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{5DBF8A7C-4F69-4778-B446-4FD13850CE7C}" name="Total Cumulative Inventory Items" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{FAB7F246-DBFE-48B7-9D0E-62F04D72EF5E}" name="Total Cumulative Maintenance Hours" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{3FAA3011-47B9-49E2-BE83-98BABA45CEF4}" name="Average Theater Intensity Ratio" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{AD53D50A-40C7-4504-85C0-88E6A1BF1A92}" name="Theater Readiness Assessment" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1224,22 +1224,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="E1" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>8</v>
-      </c>
       <c r="F1" s="8" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1259,7 +1259,7 @@
         <v>5.72</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
@@ -1279,7 +1279,7 @@
         <v>13.92</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
@@ -1299,7 +1299,7 @@
         <v>5.45</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
@@ -1319,7 +1319,7 @@
         <v>0.77</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
